--- a/data/file_generation/input/data_57/巴西甲开赛时间_2025-10-27_03_00博塔弗戈_VS桑托斯_比分2-2(2-1)标盘明细.xlsx
+++ b/data/file_generation/input/data_57/巴西甲开赛时间_2025-10-27_03_00博塔弗戈_VS桑托斯_比分2-2(2-1)标盘明细.xlsx
@@ -35520,26 +35520,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{503418BC-268C-463D-92E9-DCD318DFC5EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF97CFB3-3292-4F8F-99B5-44F9CBDBE475}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94A58047-EC3F-47EF-B4F2-443CF31548F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D45814E-8670-4463-A43E-EB8D63FFD0FB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85D57E4E-CC80-44AC-8A96-8375F543E7D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DA0AD7E-5596-4EDD-90FC-CB467FF5F9F7}"/>
 </file>